--- a/AZ_public_ECE_contacts.xlsx
+++ b/AZ_public_ECE_contacts.xlsx
@@ -603,8 +603,16 @@
           <t>Director of Early Learning</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr"/>
-      <c r="K4" s="3" t="inlineStr"/>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>albullockgrotting@mpsaz.org</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
           <t>480-472-1011</t>
@@ -747,8 +755,16 @@
           <t>Executive Director of PK-12 Curriculum and Instruction</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr"/>
-      <c r="K6" s="3" t="inlineStr"/>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>jessica.edgar@cusd80.com</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
           <t>480-812-7000</t>
@@ -764,7 +780,7 @@
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t>Dr. Edgar has 22 years in CUSD80. Email domain is cusd80.com. Email needed — check Apollo.io.</t>
+          <t>Email format first.last@cusd80.com confirmed as district pattern. Phone: 480-224-3716.</t>
         </is>
       </c>
     </row>
@@ -812,8 +828,16 @@
           <t>Director of K-12 Curriculum and Instruction</t>
         </is>
       </c>
-      <c r="J7" s="4" t="inlineStr"/>
-      <c r="K7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>ngillispie@peoriaud.k12.az.us</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
           <t>623-486-6000</t>
@@ -833,7 +857,7 @@
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>Email domain is peoriaud.k12.az.us. Email needed — check Apollo.io.</t>
+          <t>Email format inferred from peoriaud.k12.az.us domain pattern confirmed via secondary source (ZoomInfo).</t>
         </is>
       </c>
     </row>
@@ -881,8 +905,16 @@
           <t>Early Childhood Manager</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr"/>
-      <c r="K8" s="3" t="inlineStr"/>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>jzeek@dvusd.org</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
           <t>602-467-6013</t>
@@ -902,7 +934,7 @@
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t>Programs include Head Start and Community Education Preschool. Email needed — check Apollo.io.</t>
+          <t>Email format inferred from dvusd.org domain. Programs include Head Start and Community Education Preschool.</t>
         </is>
       </c>
     </row>
@@ -1008,21 +1040,9 @@
           <t>15002 N 32nd Street, Phoenix, AZ 85032</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>Jean</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>Koeppen</t>
-        </is>
-      </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>Assistant Superintendent of Curriculum, Instruction and Assessment</t>
-        </is>
-      </c>
+      <c r="G10" s="3" t="inlineStr"/>
+      <c r="H10" s="3" t="inlineStr"/>
+      <c r="I10" s="3" t="inlineStr"/>
       <c r="J10" s="3" t="inlineStr"/>
       <c r="K10" s="3" t="inlineStr"/>
       <c r="L10" s="3" t="inlineStr">
@@ -1040,7 +1060,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t>Preschool managed by Community Education Department. Email needed — check Apollo.io.</t>
+          <t>Jean Koeppen (Asst Supt Curriculum) passed away March 27, 2026. Current curriculum leadership not yet confirmed. Contact district office for updated ECE/curriculum contact: 602-449-2000.</t>
         </is>
       </c>
     </row>
@@ -1088,8 +1108,16 @@
           <t>ESS Coordinator</t>
         </is>
       </c>
-      <c r="J11" s="4" t="inlineStr"/>
-      <c r="K11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>srose@dysart.org</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
           <t>623-876-7022</t>
@@ -1219,11 +1247,31 @@
           <t>3200 W Cholla Street, Phoenix, AZ 85029</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr"/>
-      <c r="H13" s="4" t="inlineStr"/>
-      <c r="I13" s="4" t="inlineStr"/>
-      <c r="J13" s="4" t="inlineStr"/>
-      <c r="K13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>Diana</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Howsden</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>Head Start Director</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>dhowsden@wesdschools.org</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L13" s="4" t="inlineStr"/>
       <c r="M13" s="4" t="inlineStr">
         <is>
@@ -1239,7 +1287,7 @@
       </c>
       <c r="Q13" s="4" t="inlineStr">
         <is>
-          <t>Largest elementary-only district in AZ. Runs Head Start Plus program. Contact Academic Services for ECE director.</t>
+          <t>Largest elementary-only district in AZ. Runs Head Start Plus program. Email pattern inferred from wesdschools.org domain confirmed via secondary source.</t>
         </is>
       </c>
     </row>
@@ -1547,8 +1595,16 @@
           <t>Preschool Teacher Director</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr"/>
-      <c r="K18" s="3" t="inlineStr"/>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>mhanks@amphi.com</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
           <t>520-696-5367</t>
@@ -1568,7 +1624,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t>Superintendent Todd Jaeger. DHS-licensed programs across multiple sites. Preschool scholarships available. Email needed — check Apollo.io.</t>
+          <t>Email format inferred from amphi.com domain (first initial + last confirmed via secondary source). Superintendent Todd Jaeger. DHS-licensed programs.</t>
         </is>
       </c>
     </row>
@@ -1616,8 +1672,16 @@
           <t>Director of Community Education</t>
         </is>
       </c>
-      <c r="J19" s="4" t="inlineStr"/>
-      <c r="K19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>rsterr@lesd79.org</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
           <t>623-535-6000</t>
@@ -1633,7 +1697,7 @@
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>Half-day and full-day ADHS/BCCL licensed PreK programs. Email needed — check Apollo.io.</t>
+          <t>Email format inferred from lesd79.org domain. Phone: 623-535-6042. Half-day and full-day ADHS/BCCL licensed PreK programs.</t>
         </is>
       </c>
     </row>
@@ -1668,9 +1732,21 @@
       </c>
       <c r="G20" s="3" t="inlineStr"/>
       <c r="H20" s="3" t="inlineStr"/>
-      <c r="I20" s="3" t="inlineStr"/>
-      <c r="J20" s="3" t="inlineStr"/>
-      <c r="K20" s="3" t="inlineStr"/>
+      <c r="I20" s="3" t="inlineStr">
+        <is>
+          <t>Preschool Programs Contact</t>
+        </is>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>ebrasher@musd20.org</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
           <t>520-568-5100</t>
@@ -1690,7 +1766,7 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t>Fast-growing district. Offers Community Preschool, Developmental Preschool, and Dual Language Preschool. ECE director name not found in public sources.</t>
+          <t>Fast-growing district. Offers Community Preschool, Developmental Preschool, and Dual Language Preschool. ebrasher is the listed preschool contact on district website; ECE director name not publicly listed.</t>
         </is>
       </c>
     </row>
@@ -1855,21 +1931,29 @@
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Lurinda</t>
+          <t>Duane</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>Ward</t>
+          <t>Sheppard</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Director of Learning Services</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr"/>
-      <c r="K23" s="4" t="inlineStr"/>
+          <t>Associate Superintendent of Curriculum &amp; Instruction</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>dsheppard2@yuma.org</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
           <t>928-502-4300</t>
@@ -1889,7 +1973,7 @@
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>Superintendent Denis Ponder (dponder@yuma.org). Duane Sheppard is Assoc Supt of Curriculum &amp; Instruction. Email needed — check Apollo.io.</t>
+          <t>Superintendent Denis Ponder (dponder@yuma.org). Lurinda Ward is Director of Learning Services (phone: 928-502-4394, email not publicly listed).</t>
         </is>
       </c>
     </row>
@@ -2010,8 +2094,16 @@
           <t>Assistant Superintendent for Curriculum and Instruction</t>
         </is>
       </c>
-      <c r="J25" s="4" t="inlineStr"/>
-      <c r="K25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>lhuffman@fusd1.org</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
           <t>928-527-6000</t>
@@ -2027,7 +2119,7 @@
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>Superintendent Michael Penca. Email needed — check Apollo.io.</t>
+          <t>Email format inferred from fusd1.org domain (pattern confirmed via secondary sources). Superintendent Michael Penca.</t>
         </is>
       </c>
     </row>
@@ -2339,8 +2431,16 @@
           <t>Superintendent</t>
         </is>
       </c>
-      <c r="J30" s="3" t="inlineStr"/>
-      <c r="K30" s="3" t="inlineStr"/>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>gdorner@kusd.org</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
           <t>928-753-5678</t>
@@ -2360,7 +2460,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t>Multiple preschool sites: Desert Willow, Manzanita North, Mt. Tipton. National Accreditation Commission certified. No specific ECE director found.</t>
+          <t>Superintendent email confirmed. Multiple preschool sites: Desert Willow, Manzanita North, Mt. Tipton. National Accreditation Commission certified.</t>
         </is>
       </c>
     </row>
@@ -2408,10 +2508,14 @@
           <t>Director of Early Childhood Learning</t>
         </is>
       </c>
-      <c r="J31" s="4" t="inlineStr"/>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>cassandra.goldberg@cgesd.org</t>
+        </is>
+      </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2429,7 +2533,7 @@
       </c>
       <c r="Q31" s="4" t="inlineStr">
         <is>
-          <t>Contact found via ZoomInfo. Email domain likely cgesd.org but not confirmed on official site. Email needed — verify via Apollo.io.</t>
+          <t>Email confirmed on official CGESD Early Childhood Learning Center contact page.</t>
         </is>
       </c>
     </row>
@@ -2608,11 +2712,31 @@
           <t>295 W Western Ave, Avondale, AZ 85323</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr"/>
-      <c r="H34" s="3" t="inlineStr"/>
-      <c r="I34" s="3" t="inlineStr"/>
-      <c r="J34" s="3" t="inlineStr"/>
-      <c r="K34" s="3" t="inlineStr"/>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>Eric</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>Dueppen</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>superintendent@chooseaesd.org</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
           <t>623-772-5000</t>
@@ -2628,7 +2752,7 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t>K-8 district. PreK programs offered but ECE director not publicly listed.</t>
+          <t>K-8 district. Departmental superintendent email confirmed on chooseaesd.org/leadership. For ECE-specific contact, contact Academic Services through this address.</t>
         </is>
       </c>
     </row>
@@ -2726,11 +2850,31 @@
           <t>25555 Durango St, Buckeye, AZ 85326</t>
         </is>
       </c>
-      <c r="G36" s="3" t="inlineStr"/>
-      <c r="H36" s="3" t="inlineStr"/>
-      <c r="I36" s="3" t="inlineStr"/>
-      <c r="J36" s="3" t="inlineStr"/>
-      <c r="K36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>Ana</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>Gutierrez</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>Executive Director of Curriculum and Assessment</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>CIA@besd33.org</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
           <t>623-925-3400</t>
@@ -2746,7 +2890,7 @@
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t>9 schools. Superintendent: Dr. Lanese (since Jan 2024). Curriculum director not publicly listed.</t>
+          <t>Departmental curriculum email confirmed on besd33.org. Dr. Lanese is superintendent (since Jan 2024).</t>
         </is>
       </c>
     </row>
@@ -2854,24 +2998,32 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>Kevin</t>
+          <t>Sue</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t>Stoltzfus</t>
+          <t>Shinn</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Superintendent</t>
-        </is>
-      </c>
-      <c r="J38" s="3" t="inlineStr"/>
-      <c r="K38" s="3" t="inlineStr"/>
+          <t>Director, Emily Meschter Early Learning Center</t>
+        </is>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>sue.shinn@fwusd.org</t>
+        </is>
+      </c>
+      <c r="K38" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t>520-696-8800</t>
+          <t>520-696-8909</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
@@ -2888,7 +3040,7 @@
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t>Emily Meschter Early Learning Center (Teddy Bears) for PreK. Admin Asst Paula Alden (520-696-8801). 11 schools total.</t>
+          <t>Preschool director confirmed on district site. Center at 4605 N La Cholla Blvd, Tucson, AZ 85705. Superintendent Kevin Stoltzfus (kevin.stoltzfus@fwusd.org). Note: domain is @fwusd.org, not @flowingwellsschools.org.</t>
         </is>
       </c>
     </row>
@@ -2918,17 +3070,37 @@
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Prescott Valley, AZ</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr"/>
-      <c r="H39" s="4" t="inlineStr"/>
-      <c r="I39" s="4" t="inlineStr"/>
-      <c r="J39" s="4" t="inlineStr"/>
-      <c r="K39" s="4" t="inlineStr"/>
+          <t>8601 E Loos Dr, Prescott Valley, AZ 86314</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr">
+        <is>
+          <t>Stephanie</t>
+        </is>
+      </c>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>Rowe</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>Director of Pre-K Program</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>stephanie.rowe@humboldtunified.com</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>928-759-4000</t>
+          <t>928-759-5130</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr"/>
@@ -2941,7 +3113,7 @@
       </c>
       <c r="Q39" s="4" t="inlineStr">
         <is>
-          <t>Diane Sallinger is Math &amp; ELA Curriculum Coordinator. No specific ECE director identified. Email needed — check Apollo.io.</t>
+          <t>Pre-K Director confirmed on district site. Located at 8601 E Loos Dr, Prescott Valley, AZ 86314. Phone: 928-759-5130. Diane Sallinger is Curriculum Coordinator (diane.sallinger@humboldtunified.com).</t>
         </is>
       </c>
     </row>
@@ -3586,8 +3758,16 @@
           <t>Director of Leadership &amp; Learning</t>
         </is>
       </c>
-      <c r="J49" s="4" t="inlineStr"/>
-      <c r="K49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>tfountain@jocombs.org</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
           <t>480-987-5308</t>
@@ -3603,7 +3783,7 @@
       </c>
       <c r="Q49" s="4" t="inlineStr">
         <is>
-          <t>Nationally recognized District of Distinction. Specific ECE director not identified. Email needed — check Apollo.io.</t>
+          <t>Email confirmed on jocombs.org staff directory. Phone: 480-987-5300 ext 5308. Nationally recognized District of Distinction.</t>
         </is>
       </c>
     </row>
@@ -3839,11 +4019,31 @@
           <t>734 W 11th St, Safford, AZ 85546</t>
         </is>
       </c>
-      <c r="G53" s="4" t="inlineStr"/>
-      <c r="H53" s="4" t="inlineStr"/>
-      <c r="I53" s="4" t="inlineStr"/>
-      <c r="J53" s="4" t="inlineStr"/>
-      <c r="K53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr">
+        <is>
+          <t>Kent</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Baldwin</t>
+        </is>
+      </c>
+      <c r="I53" s="4" t="inlineStr">
+        <is>
+          <t>Director of Instructional Services</t>
+        </is>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
+        <is>
+          <t>kbaldwin@saffordusd.com</t>
+        </is>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
           <t>928-348-7000</t>
@@ -3863,7 +4063,7 @@
       </c>
       <c r="Q53" s="4" t="inlineStr">
         <is>
-          <t>Rebecca Hale is Lead PreK Teacher for low-income families. Dr. Katherine Kuhn is Principal. District seeking curriculum for low-income students.</t>
+          <t>Email confirmed in Safford USD staff directory. Curriculum overhaul underway 2025. Rebecca Hale is Lead PreK Teacher.</t>
         </is>
       </c>
     </row>
@@ -4349,8 +4549,16 @@
           <t>Superintendent</t>
         </is>
       </c>
-      <c r="J60" s="3" t="inlineStr"/>
-      <c r="K60" s="3" t="inlineStr"/>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>hollism@snowflake.k12.az.us</t>
+        </is>
+      </c>
+      <c r="K60" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L60" s="3" t="inlineStr">
         <is>
           <t>928-536-4156</t>
@@ -4633,8 +4841,16 @@
           <t>Superintendent</t>
         </is>
       </c>
-      <c r="J64" s="3" t="inlineStr"/>
-      <c r="K64" s="3" t="inlineStr"/>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>shagerman@tanqueverdeschools.org</t>
+        </is>
+      </c>
+      <c r="K64" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L64" s="3" t="inlineStr">
         <is>
           <t>520-749-5751</t>
@@ -4702,8 +4918,16 @@
           <t>Assistant Superintendent of Academic and Special Services</t>
         </is>
       </c>
-      <c r="J65" s="4" t="inlineStr"/>
-      <c r="K65" s="4" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>ksacco@pusd10.org</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L65" s="4" t="inlineStr">
         <is>
           <t>928-474-5161</t>
@@ -4723,7 +4947,7 @@
       </c>
       <c r="Q65" s="4" t="inlineStr">
         <is>
-          <t>PK-12 district. Email needed — check Apollo.io.</t>
+          <t>Email format inferred from pusd10.org domain (pattern confirmed via secondary source). Phone: 928-472-5800.</t>
         </is>
       </c>
     </row>
@@ -4771,10 +4995,14 @@
           <t>Director of Curriculum &amp; Instruction</t>
         </is>
       </c>
-      <c r="J66" s="3" t="inlineStr"/>
+      <c r="J66" s="3" t="inlineStr">
+        <is>
+          <t>zainulabuddin@balsz.org</t>
+        </is>
+      </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L66" s="3" t="inlineStr">
@@ -4792,7 +5020,7 @@
       </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>Superintendent: Dr. George J. Barnes. 6 schools including Orangedale Early Learning Center. Email needed — check Apollo.io.</t>
+          <t>Superintendent: Dr. George J. Barnes. 6 schools including Orangedale Early Learning Center. Email inferred from last name + domain pattern.</t>
         </is>
       </c>
     </row>
@@ -4861,7 +5089,7 @@
       </c>
       <c r="Q67" s="4" t="inlineStr">
         <is>
-          <t>PK-12 district. Superintendent serves as ECE contact. Email needed — check Apollo.io.</t>
+          <t>Amber Martinez became superintendent July 1, 2025 — new leadership. PK-12 district. Email needed — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -5032,9 +5260,21 @@
           <t>1 N Willard St, Cottonwood, AZ 86326</t>
         </is>
       </c>
-      <c r="G70" s="3" t="inlineStr"/>
-      <c r="H70" s="3" t="inlineStr"/>
-      <c r="I70" s="3" t="inlineStr"/>
+      <c r="G70" s="3" t="inlineStr">
+        <is>
+          <t>Jessica</t>
+        </is>
+      </c>
+      <c r="H70" s="3" t="inlineStr">
+        <is>
+          <t>Vocca</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
       <c r="J70" s="3" t="inlineStr"/>
       <c r="K70" s="3" t="inlineStr"/>
       <c r="L70" s="3" t="inlineStr">
@@ -5052,7 +5292,7 @@
       </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
-          <t>Cottonwood Education Services preschool with 93 ECE students. ECE director contact not found.</t>
+          <t>Jessica Vocca became superintendent April 1, 2025. New leadership. Cottonwood Education Services preschool with 93 ECE students. Email needed — check Apollo.io.</t>
         </is>
       </c>
     </row>
@@ -5284,11 +5524,31 @@
           <t>8450 S Olive Ave, Mohave Valley, AZ 86440</t>
         </is>
       </c>
-      <c r="G74" s="3" t="inlineStr"/>
-      <c r="H74" s="3" t="inlineStr"/>
-      <c r="I74" s="3" t="inlineStr"/>
-      <c r="J74" s="3" t="inlineStr"/>
-      <c r="K74" s="3" t="inlineStr"/>
+      <c r="G74" s="3" t="inlineStr">
+        <is>
+          <t>Cole</t>
+        </is>
+      </c>
+      <c r="H74" s="3" t="inlineStr">
+        <is>
+          <t>Young</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>youngc@mvdistrict.net</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L74" s="3" t="inlineStr">
         <is>
           <t>928-768-2507</t>
@@ -5304,7 +5564,7 @@
       </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
-          <t>Elementary district (PK-8). Staff directory available on website. ECE director not identified.</t>
+          <t>Email confirmed on official district admin page. Note: email domain is mvdistrict.net (not mvesd16.org).</t>
         </is>
       </c>
     </row>
@@ -5337,11 +5597,31 @@
           <t>1090 S Vulture Mine Road, Wickenburg, AZ 85390</t>
         </is>
       </c>
-      <c r="G75" s="4" t="inlineStr"/>
-      <c r="H75" s="4" t="inlineStr"/>
-      <c r="I75" s="4" t="inlineStr"/>
-      <c r="J75" s="4" t="inlineStr"/>
-      <c r="K75" s="4" t="inlineStr"/>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>Barbara</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>Remondini</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>bremondini@wusd9.org</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L75" s="4" t="inlineStr">
         <is>
           <t>928-684-6600</t>
@@ -5357,7 +5637,7 @@
       </c>
       <c r="Q75" s="4" t="inlineStr">
         <is>
-          <t>Superintendent: Dr. Michael Sivertson. Preschool at Festival Foothills and Hassayampa Elementary. Email needed — check Apollo.io.</t>
+          <t>Dr. Barbara Remondini is current superintendent (domain wusd9.org). Dr. Michael Sivertson is superintendent-designate (incoming). Preschool at Festival Foothills and Hassayampa Elementary.</t>
         </is>
       </c>
     </row>
@@ -5478,8 +5758,16 @@
           <t>Superintendent</t>
         </is>
       </c>
-      <c r="J77" s="4" t="inlineStr"/>
-      <c r="K77" s="4" t="inlineStr"/>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>ndettmar@msdaz.org</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
           <t>602-353-5004</t>
@@ -5616,8 +5904,16 @@
           <t>Assistant Superintendent</t>
         </is>
       </c>
-      <c r="J79" s="4" t="inlineStr"/>
-      <c r="K79" s="4" t="inlineStr"/>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>emorris@busd40.org</t>
+        </is>
+      </c>
+      <c r="K79" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
       <c r="L79" s="4" t="inlineStr">
         <is>
           <t>520-719-1200</t>
@@ -5633,7 +5929,7 @@
       </c>
       <c r="Q79" s="4" t="inlineStr">
         <is>
-          <t>Serves Tohono O'odham Nation. PK-12 with cultural Himdag integration. 6 schools. 100% minority enrollment.</t>
+          <t>Email format inferred from busd40.org domain pattern (first initial + last). Serves Tohono O'odham Nation. PK-12 with cultural Himdag integration.</t>
         </is>
       </c>
     </row>
@@ -5743,13 +6039,17 @@
       </c>
       <c r="I81" s="4" t="inlineStr">
         <is>
-          <t>Teaching and Learning Associate Superintendent</t>
-        </is>
-      </c>
-      <c r="J81" s="4" t="inlineStr"/>
+          <t>Associate Superintendent, Federal Programs</t>
+        </is>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>rgutierrez@riverside.k12.az.us</t>
+        </is>
+      </c>
       <c r="K81" s="4" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="L81" s="4" t="inlineStr">
@@ -5767,7 +6067,7 @@
       </c>
       <c r="Q81" s="4" t="inlineStr">
         <is>
-          <t>Superintendent: Dr. Jaime A. Rivera. 2 main campuses. Email needed — check Apollo.io.</t>
+          <t>Superintendent: Dr. Jaime A. Rivera. Gutierrez oversees federal programs including Title I PreK. 2 main campuses.</t>
         </is>
       </c>
     </row>
@@ -5873,11 +6173,31 @@
           <t>519 W Melody Lane, Bisbee, AZ 85603</t>
         </is>
       </c>
-      <c r="G83" s="4" t="inlineStr"/>
-      <c r="H83" s="4" t="inlineStr"/>
-      <c r="I83" s="4" t="inlineStr"/>
-      <c r="J83" s="4" t="inlineStr"/>
-      <c r="K83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr">
+        <is>
+          <t>Jennifer</t>
+        </is>
+      </c>
+      <c r="H83" s="4" t="inlineStr">
+        <is>
+          <t>McBeth</t>
+        </is>
+      </c>
+      <c r="I83" s="4" t="inlineStr">
+        <is>
+          <t>Superintendent</t>
+        </is>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>jmcbeth@busd.k12.az.us</t>
+        </is>
+      </c>
+      <c r="K83" s="4" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
       <c r="L83" s="4" t="inlineStr">
         <is>
           <t>520-432-5381</t>
@@ -5893,7 +6213,7 @@
       </c>
       <c r="Q83" s="4" t="inlineStr">
         <is>
-          <t>Small district (675 students, 4 schools). No dedicated ECE director. Contact main office for PreK info.</t>
+          <t>Superintendent email confirmed. Small district (675 students, 4 schools).</t>
         </is>
       </c>
     </row>
@@ -5941,8 +6261,16 @@
           <t>Superintendent</t>
         </is>
       </c>
-      <c r="J84" s="3" t="inlineStr"/>
-      <c r="K84" s="3" t="inlineStr"/>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>eevans@wusd2.org</t>
+        </is>
+      </c>
+      <c r="K84" s="3" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
       <c r="L84" s="3" t="inlineStr">
         <is>
           <t>928-635-4474</t>
@@ -5958,7 +6286,7 @@
       </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
-          <t>Small rural district with 2 schools. Limited ECE program info available. Email needed — check Apollo.io.</t>
+          <t>Email inferred from wusd2.org domain pattern. Phone: 928-635-4473. Small rural district with 2 schools.</t>
         </is>
       </c>
     </row>
@@ -6096,7 +6424,7 @@
       </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
-          <t>Very small district (335 students, 2 schools). Superintendent serves as ECE contact.</t>
+          <t>Stephen Estatico resigned January 1, 2026. William Duarte served as interim superintendent. Leadership in transition — verify current superintendent before outreach.</t>
         </is>
       </c>
     </row>
